--- a/splitters_kolpinskoe_127_129_v6.xlsx
+++ b/splitters_kolpinskoe_127_129_v6.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Каскады" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +69,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,6 +192,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3339,4 +3349,1002 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="21" min="1" max="1"/>
+    <col width="7" customWidth="1" style="21" min="2" max="2"/>
+    <col width="11" customWidth="1" style="21" min="3" max="3"/>
+    <col width="11" customWidth="1" style="21" min="4" max="4"/>
+    <col width="10" customWidth="1" style="21" min="5" max="5"/>
+    <col width="120" customWidth="1" style="21" min="6" max="6"/>
+    <col width="9" customWidth="1" style="21" min="7" max="7"/>
+    <col width="9" customWidth="1" style="21" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>РАСКЛАДКА КАСКАДОВ — 24 шт. × 32 порта = 768 портов, пустых 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Каскад 1</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>Каскад 2</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Дом</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>Состав каскада 2 (делители и их порты по парадным)</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>Портов</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t>Пустых</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.1 + д.127 п.3 + д.127 п.6 + д.127 п.7</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.8 + д.127 п.10 + д.127 п.10 + д.127 п.12</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H5" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.12 + д.127 п.12 + д.127 п.14 + д.127 п.14</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.14 + д.127 п.16 + д.127 п.16 + д.127 п.17</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.18 + д.127 п.19 + д.127 п.20 + д.127 п.21</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.22 + д.127 п.22 + д.127 п.23 + д.127 п.23</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.1 + д.129 п.3 + д.129 п.4 + д.129 п.5</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.6 + д.129 п.6 + д.129 п.7 + д.129 п.8</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.8 + д.129 п.9 + д.129 п.10 + д.129 п.12</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>4→8</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>1×4</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>4 × 1×8</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.15 + д.129 п.15 + д.129 п.16 + д.129 п.16</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.1(4п) + д.127 п.1(4п) + д.127 п.1(4п) + д.127 п.1(1п)/2(3п) + д.127 п.2(4п) + д.127 п.2(4п) + д.127 п.2(4п) + д.127 п.3(4п)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.3(4п) + д.127 п.3(2п)/4(2п) + д.127 п.4(4п) + д.127 п.4(3п)/5(1п) + д.127 п.5(4п) + д.127 п.5(4п) + д.127 п.6(4п) + д.127 п.6(4п)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.6(4п) + д.127 п.6(3п)/7(1п) + д.127 п.7(4п) + д.127 п.7(4п) + д.127 п.7(4п) + д.127 п.7(2п)/8(2п) + д.127 п.8(4п) + д.127 п.8(4п)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.8(3п)/9(1п) + д.127 п.9(4п) + д.127 п.9(4п) + д.127 п.9(4п) + д.127 п.9(2п)/10(2п) + д.127 п.10(4п) + д.127 п.10(4п) + д.127 п.10(1п)/11(3п)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.11(4п) + д.127 п.11(1п)/12(3п) + д.127 п.12(4п) + д.127 п.13(4п) + д.127 п.13(4п) + д.127 п.13(4п) + д.127 п.14(4п) + д.127 п.14(3п)/15(1п)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.15(4п) + д.127 п.15(3п)/16(1п) + д.127 п.16(4п) + д.127 п.16(4п) + д.127 п.16(2п)/17(2п) + д.127 п.17(4п) + д.127 п.17(3п)/18(1п) + д.127 п.18(4п)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.18(4п) + д.127 п.18(1п)/19(3п) + д.127 п.19(4п) + д.127 п.19(4п) + д.127 п.19(4п) + д.127 п.20(4п) + д.127 п.20(4п) + д.127 п.20(4п)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.20(2п)/21(2п) + д.127 п.21(4п) + д.127 п.21(4п) + д.127 п.21(2п)/22(2п) + д.127 п.22(4п) + д.127 п.22(4п) + д.127 п.22(3п)/23(1п) + д.127 п.23(4п)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H21" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>127+129</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>д.127 п.23(4п) + д.129 п.13(1п)/14(3п) + д.129 п.14(4п) + д.129 п.14(2п)/15(2п) + д.129 п.15(4п) + д.129 п.15(3п)/16(1п) + д.129 п.16(4п) + д.129 п.16(4п)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H22" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.1(4п) + д.129 п.1(4п) + д.129 п.1(4п) + д.129 п.2(4п) + д.129 п.2(4п) + д.129 п.2(4п) + д.129 п.2(4п) + д.129 п.3(4п)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H23" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.3(4п) + д.129 п.3(4п) + д.129 п.3(1п)/4(3п) + д.129 п.4(4п) + д.129 п.4(4п) + д.129 п.4(2п)/5(2п) + д.129 п.5(4п) + д.129 п.5(4п)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.5(4п) + д.129 п.6(4п) + д.129 п.6(4п) + д.129 п.6(4п) + д.129 п.6(2п)/7(2п) + д.129 п.7(4п) + д.129 п.7(4п) + д.129 п.7(3п)/8(1п)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H25" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.8(4п) + д.129 п.8(4п) + д.129 п.8(4п) + д.129 п.8(1п)/9(3п) + д.129 п.9(4п) + д.129 п.9(4п) + д.129 п.9(3п)/10(1п) + д.129 п.10(4п)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>8→4</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>1×8</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>8 × 1×4</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
+        <is>
+          <t>д.129 п.10(4п) + д.129 п.10(1п)/11(3п) + д.129 п.11(4п) + д.129 п.11(2п)/12(2п) + д.129 п.12(4п) + д.129 п.12(4п) + д.129 п.13(4п) + д.129 п.13(4п)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>14 шт. 8→4 + 10 шт. 4→8</t>
+        </is>
+      </c>
+      <c r="G29" s="29">
+        <f>24*32</f>
+        <v/>
+      </c>
+      <c r="H29" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Делители каскада 1: 14 шт. 1×8 (схема 8→4) + 10 шт. 1×4 (схема 4→8) = 24 шт., по одному на PON-порт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Делители каскада 2 (абонентские): 112 шт. 1×4 + 40 шт. 1×8. Все выходы задействованы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ВСЕГО оборудования: 1×4 — 122 шт. (112 абон. + 10 каскадных), 1×8 — 54 шт. (40 абон. + 14 каскадных).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Запись «п.6(3п)/7(1п)» — делитель 1×4 расшарен между парадными: 3 порта в п.6 и 1 порт в п.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Каскад №19 — единственный, идущий через оба дома (1 делитель в д.127 п.23 + 7 в д.129).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Порядок делителей внутри группы можно менять как удобно по трассе — на кратность и пустые порты это не влияет.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>